--- a/astro-site/public/dl/kit-tareas-bar/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/BONUS-02-calendario-anual-tareas.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -119,49 +121,49 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -521,15 +523,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -537,6 +540,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -558,8 +562,25 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -568,17 +589,17 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="18"/>
-    <col customWidth="1" max="3" min="3" width="25"/>
-    <col customWidth="1" max="4" min="4" width="40"/>
-    <col customWidth="1" max="5" min="5" width="15"/>
-    <col customWidth="1" max="6" min="6" width="30"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -588,6 +609,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1164,6 +1186,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
@@ -1175,6 +1198,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-bar/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-bar/BONUS-02-calendario-anual-tareas.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Calendario Anual'!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +78,22 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +110,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,6 +185,53 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,48 +598,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>BONUS 02 — Calendario Anual · Bar / Cocktails</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Fechas clave para bares con tareas asociadas.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>▸ Cada fecha incluye qué preparar y con cuánta antelación</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>▸ Añade las fechas locales de tu zona</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
+      <c r="B8" s="3" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (barra).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>▸ Estás en BONUS-02-calendario-anual-tareas.xlsx: es una capa MÁS, no una repetición — el marco del día está en 08-apertura-cierre-negocio.xlsx y 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="35" customHeight="1">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-bar · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -591,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -643,558 +784,751 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>1 Enero</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Año Nuevo</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Decidir si se abre; si se cierra, comunicarlo en Google Business Profile y en RRSS con una semana</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>La madrugada del 1 es la resaca de la noche más fuerte del año</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>14 Febrero</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>San Valentín</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>Cócteles para parejas, carta especial, decoración</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>Reforzar servicio de mesa</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Feb-Mar</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Carnaval</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Cócteles temáticos, decoración, horario ampliado y control de aforo con disfraces</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Variable según zona; en muchas ciudades es la noche del año</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>17 Marzo</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>St. Patrick's Day</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>Stock extra de cerveza, whisky irlandés, decoración verde</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>Evento muy potente para bares</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Mar-Abr</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>Semana Santa</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Ajustar horarios, cócteles de temporada</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>Variable según zona</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>1 Mayo</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Día del Trabajo y puentes de primavera</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>Horario de festivo, terraza a pleno rendimiento y stock para varios días seguidos</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="inlineStr">
+        <is>
+          <t>Un puente mueve más que un sábado normal y se pide con el mismo plazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>5 Mayo</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>Cinco de Mayo</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Margaritas, mezcal, tequila, decoración mexicana</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>Tendencia en crecimiento</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>21 Junio</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Solsticio / Inicio Verano</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>Cócteles refrescantes, terraza a tope</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>Abrir temporada de terraza</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>Jun-Sep</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Temporada Verano</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>Mojitos, gin tonics, spritz, cócteles con fruta</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>4 semanas</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>Stock extra de hielo y cítricos</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>15 Agosto</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Asunción y fiestas de agosto</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>Servicio de festivo, refuerzo de turnos y stock extra de hielo y cítricos</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>Muchas fiestas patronales caen esa semana: mira el calendario local</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>31 Octubre</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>Halloween</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>Cócteles temáticos, decoración, hielo seco</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t>Noche fuerte de facturación</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Beaujolais Nouveau</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>Vino nuevo, maridaje</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>Para bares de vino</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>6-8 Diciembre</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Puente de la Constitución y la Inmaculada</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Horario de festivo, refuerzo de mediodía y stock para tres días seguidos</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Arranca de hecho la temporada de cenas de empresa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>Navidad/Empresas</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D17" s="28" t="inlineStr">
         <is>
           <t>Cenas de empresa, barra libre, carta especial</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>4 semanas</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>Pico máximo del año para bares</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>24 Diciembre</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Nochebuena</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Decidir el horario (muchos bares cierran la tarde y abren sólo la madrugada), turno reducido y comunicar el horario del día en Google Business Profile y en RRSS</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>3 semanas</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>La copa de después de la cena familiar es un pico corto y muy rentable</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>31 Diciembre</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>Nochevieja</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D19" s="28" t="inlineStr">
         <is>
           <t>Champagne, cava, fiesta, entrada con consumición</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>3 semanas</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F19" s="29" t="inlineStr">
         <is>
           <t>La noche MÁS importante</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>Fiestas Locales</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>Adaptar carta y horarios a fiestas patronales</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>3 semanas</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
         <is>
           <t>AÑADE TUS FECHAS LOCALES</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>Eventos Deportivos</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>Stock extra cerveza, pantallas, horarios especiales</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F21" s="29" t="inlineStr">
         <is>
           <t>Champions, Eurocopa, Mundial</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>World Cocktail Day (13 May)</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>World Cocktail Day (13 de mayo)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>Cóctel gratis, taller, promo RRSS</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>Marketing y branding</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Negroni Week (Sep)</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Negroni Week (septiembre)</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
         <is>
           <t>Carta de Negronis, donación benéfica por cóctel</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F23" s="29" t="inlineStr">
         <is>
           <t>Evento global de coctelería</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>After-Work Semanal</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>Happy hour recurrente, fidelización</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>Fijo</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F24" s="24" t="inlineStr">
         <is>
           <t>Programa de fidelización</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>Catas y Maridajes</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>Cata guiada mensual (vinos, spirits, cócteles)</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>3 semanas</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F25" s="29" t="inlineStr">
         <is>
           <t>Diferenciación y premium</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>DJ / Música en Vivo</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>Sonido, decoración, stock extra, aforo</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>Control de ruido vecinal</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Bar / Cocktails · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
